--- a/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t>销售单号</t>
   </si>
@@ -266,7 +266,10 @@
     <t>{.shopName}</t>
   </si>
   <si>
-    <t>{.logistics.logisticsChannelName}</t>
+    <t>{.logisticsChannelName}</t>
+  </si>
+  <si>
+    <t>{.shippingCost}</t>
   </si>
 </sst>
 </file>
@@ -1207,7 +1210,7 @@
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="3" max="3" width="15.25" customWidth="1"/>
     <col min="4" max="4" width="17.375" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="12.875" customWidth="1"/>
     <col min="8" max="8" width="18.625" customWidth="1"/>
     <col min="9" max="9" width="14.625" customWidth="1"/>
@@ -1448,7 +1451,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1460,6 +1463,9 @@
       </c>
       <c r="D2" t="s">
         <v>73</v>
+      </c>
+      <c r="E2" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="138">
   <si>
     <t>销售单号</t>
   </si>
@@ -270,6 +270,195 @@
   </si>
   <si>
     <t>{.shippingCost}</t>
+  </si>
+  <si>
+    <t>{.totalProfit}</t>
+  </si>
+  <si>
+    <t>{.profitRate}</t>
+  </si>
+  <si>
+    <t>{.platformCode}</t>
+  </si>
+  <si>
+    <t>{.approveStatusName}</t>
+  </si>
+  <si>
+    <t>{.billStatusName}</t>
+  </si>
+  <si>
+    <t>{.logisticsCode}</t>
+  </si>
+  <si>
+    <t>{.amount}</t>
+  </si>
+  <si>
+    <t>{.payTime}</t>
+  </si>
+  <si>
+    <t>{.dictPayMethodName}</t>
+  </si>
+  <si>
+    <t>{.currency}</t>
+  </si>
+  <si>
+    <t>{.platformSpuNo}</t>
+  </si>
+  <si>
+    <t>{.platformSkuNo}</t>
+  </si>
+  <si>
+    <t>{.qty}</t>
+  </si>
+  <si>
+    <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.variantProperty}</t>
+  </si>
+  <si>
+    <t>{.taxCost}{.sourceCurrency}</t>
+  </si>
+  <si>
+    <t>{.sourceAmount}</t>
+  </si>
+  <si>
+    <t>{.baseAmount}</t>
+  </si>
+  <si>
+    <t>{.warehouseName}</t>
+  </si>
+  <si>
+    <t>{.warehouseLocation}</t>
+  </si>
+  <si>
+    <t>{.buyerRemark}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.categoryNames}</t>
+  </si>
+  <si>
+    <t>{.deliveryTime}</t>
+  </si>
+  <si>
+    <t>{.estimatedShippingCost}{.estimatedShippingCurrency}</t>
+  </si>
+  <si>
+    <t>{.actualShippingCost}{.actualShippingCurrency}</t>
+  </si>
+  <si>
+    <t>{.weight}g</t>
+  </si>
+  <si>
+    <t>{.accessoriesSkuNo}</t>
+  </si>
+  <si>
+    <t>{.accessoriesQty}</t>
+  </si>
+  <si>
+    <t>{.accessoriesNw}</t>
+  </si>
+  <si>
+    <t>{.accessoriesCost}</t>
+  </si>
+  <si>
+    <t>{.length}cm</t>
+  </si>
+  <si>
+    <t>{.width}cm</t>
+  </si>
+  <si>
+    <t>{.height}cm</t>
+  </si>
+  <si>
+    <t>{.loginId}</t>
+  </si>
+  <si>
+    <t>{.buyerName}</t>
+  </si>
+  <si>
+    <t>{.email}</t>
+  </si>
+  <si>
+    <t>{.telNumber}</t>
+  </si>
+  <si>
+    <t>{.firstAddress}</t>
+  </si>
+  <si>
+    <t>{.secondAddress}</t>
+  </si>
+  <si>
+    <t>{.country}</t>
+  </si>
+  <si>
+    <t>{.provinceName}</t>
+  </si>
+  <si>
+    <t>{.cityName}</t>
+  </si>
+  <si>
+    <t>{.districtName}</t>
+  </si>
+  <si>
+    <t>{.receiverName}</t>
+  </si>
+  <si>
+    <t>{.postCode}</t>
+  </si>
+  <si>
+    <t>{.receiverTelNumber}</t>
+  </si>
+  <si>
+    <t>{.fullAddress}</t>
+  </si>
+  <si>
+    <t>{.receiverTaxNo}</t>
+  </si>
+  <si>
+    <t>{.sourceFinanceAmount}</t>
+  </si>
+  <si>
+    <t>{.financeAmount}</t>
+  </si>
+  <si>
+    <t>{.sourceFinanceShippingCost}</t>
+  </si>
+  <si>
+    <t>{.financeShippingCost}</t>
+  </si>
+  <si>
+    <t>{.sourceItemCost}</t>
+  </si>
+  <si>
+    <t>{.itemCost}</t>
+  </si>
+  <si>
+    <t>{.sourceLogisticsCost}</t>
+  </si>
+  <si>
+    <t>{.logisticsCost}</t>
+  </si>
+  <si>
+    <t>{.sourcePlatformCost}</t>
+  </si>
+  <si>
+    <t>{.platformCost}</t>
+  </si>
+  <si>
+    <t>{.sourcePaypalCost}</t>
+  </si>
+  <si>
+    <t>{.paypalCost}</t>
+  </si>
+  <si>
+    <t>{.sourceVatCost}</t>
+  </si>
+  <si>
+    <t>{.vatCost}</t>
   </si>
 </sst>
 </file>
@@ -1212,6 +1401,7 @@
     <col min="4" max="4" width="17.375" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="12.875" customWidth="1"/>
+    <col min="7" max="7" width="15.125" customWidth="1"/>
     <col min="8" max="8" width="18.625" customWidth="1"/>
     <col min="9" max="9" width="14.625" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
@@ -1219,6 +1409,7 @@
     <col min="12" max="12" width="14.125" customWidth="1"/>
     <col min="13" max="13" width="13.75" customWidth="1"/>
     <col min="14" max="14" width="13.875" customWidth="1"/>
+    <col min="15" max="15" width="14.875" customWidth="1"/>
     <col min="17" max="17" width="10.5" customWidth="1"/>
     <col min="22" max="22" width="12" customWidth="1"/>
     <col min="23" max="23" width="11.875" customWidth="1"/>
@@ -1237,6 +1428,18 @@
     <col min="55" max="55" width="17.125" customWidth="1"/>
     <col min="56" max="56" width="12.125" customWidth="1"/>
     <col min="57" max="57" width="12.75" customWidth="1"/>
+    <col min="58" max="58" width="10.75" customWidth="1"/>
+    <col min="59" max="59" width="12.25" customWidth="1"/>
+    <col min="60" max="60" width="11.625" customWidth="1"/>
+    <col min="61" max="61" width="11.375" customWidth="1"/>
+    <col min="62" max="62" width="11" customWidth="1"/>
+    <col min="63" max="63" width="10.875" customWidth="1"/>
+    <col min="64" max="64" width="11.125" customWidth="1"/>
+    <col min="65" max="65" width="10.25" customWidth="1"/>
+    <col min="66" max="66" width="12.25" customWidth="1"/>
+    <col min="67" max="67" width="12.75" customWidth="1"/>
+    <col min="68" max="68" width="11.875" customWidth="1"/>
+    <col min="69" max="69" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="54" spans="1:70">
@@ -1451,7 +1654,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:70">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -1466,6 +1669,201 @@
       </c>
       <c r="E2" t="s">
         <v>74</v>
+      </c>
+      <c r="F2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N2" t="s">
+        <v>82</v>
+      </c>
+      <c r="O2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" t="s">
+        <v>86</v>
+      </c>
+      <c r="S2" t="s">
+        <v>87</v>
+      </c>
+      <c r="T2" t="s">
+        <v>88</v>
+      </c>
+      <c r="U2" t="s">
+        <v>89</v>
+      </c>
+      <c r="V2" t="s">
+        <v>90</v>
+      </c>
+      <c r="W2" t="s">
+        <v>91</v>
+      </c>
+      <c r="X2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>108</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>109</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>110</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>111</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>114</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>117</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>121</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>122</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>126</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>127</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>136</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="105">
   <si>
     <t>销售单号</t>
   </si>
@@ -44,12 +44,6 @@
     <t>运费</t>
   </si>
   <si>
-    <t>利润</t>
-  </si>
-  <si>
-    <t>利润率</t>
-  </si>
-  <si>
     <t>平台单号</t>
   </si>
   <si>
@@ -57,9 +51,6 @@
   </si>
   <si>
     <t>订单状态</t>
-  </si>
-  <si>
-    <t>买家</t>
   </si>
   <si>
     <t>物流跟踪号</t>
@@ -203,60 +194,6 @@
     <t>收件人税号</t>
   </si>
   <si>
-    <t xml:space="preserve">订单商品总售价原始币种
-</t>
-  </si>
-  <si>
-    <t>订单商品总售价人民币</t>
-  </si>
-  <si>
-    <t xml:space="preserve">运费收入原始币种
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">运费收入人民币
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">商品成本原始币种
-</t>
-  </si>
-  <si>
-    <t>商品成本人民币</t>
-  </si>
-  <si>
-    <t xml:space="preserve">物流成本原始币种
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">物流成本人民币
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">平台费原始币种
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">平台费人民币
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">转账费原始币种
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">转账费人民币
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAT税费原始币种
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VAT税费人民币
-</t>
-  </si>
-  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -272,12 +209,6 @@
     <t>{.shippingCost}</t>
   </si>
   <si>
-    <t>{.totalProfit}</t>
-  </si>
-  <si>
-    <t>{.profitRate}</t>
-  </si>
-  <si>
     <t>{.platformCode}</t>
   </si>
   <si>
@@ -296,7 +227,7 @@
     <t>{.payTime}</t>
   </si>
   <si>
-    <t>{.dictPayMethodName}</t>
+    <t>{.dictPayMethod}</t>
   </si>
   <si>
     <t>{.currency}</t>
@@ -317,7 +248,7 @@
     <t>{.variantProperty}</t>
   </si>
   <si>
-    <t>{.taxCost}{.sourceCurrency}</t>
+    <t>{.taxCost}/{.sourceCurrency}</t>
   </si>
   <si>
     <t>{.sourceAmount}</t>
@@ -329,7 +260,7 @@
     <t>{.warehouseName}</t>
   </si>
   <si>
-    <t>{.warehouseLocation}</t>
+    <t>{.warehouseLocationName}</t>
   </si>
   <si>
     <t>{.buyerRemark}</t>
@@ -344,13 +275,13 @@
     <t>{.deliveryTime}</t>
   </si>
   <si>
-    <t>{.estimatedShippingCost}{.estimatedShippingCurrency}</t>
-  </si>
-  <si>
-    <t>{.actualShippingCost}{.actualShippingCurrency}</t>
-  </si>
-  <si>
-    <t>{.weight}g</t>
+    <t>{.estimatedShippingCost}/{.estimatedShippingCurrency}</t>
+  </si>
+  <si>
+    <t>{.actualShippingCost}/{.actualShippingCurrency}</t>
+  </si>
+  <si>
+    <t>{.weight}/g</t>
   </si>
   <si>
     <t>{.accessoriesSkuNo}</t>
@@ -365,13 +296,13 @@
     <t>{.accessoriesCost}</t>
   </si>
   <si>
-    <t>{.length}cm</t>
-  </si>
-  <si>
-    <t>{.width}cm</t>
-  </si>
-  <si>
-    <t>{.height}cm</t>
+    <t>{.lengthStr}/cm</t>
+  </si>
+  <si>
+    <t>{.widthStr}/cm</t>
+  </si>
+  <si>
+    <t>{.heightStr}/cm</t>
   </si>
   <si>
     <t>{.loginId}</t>
@@ -392,7 +323,7 @@
     <t>{.secondAddress}</t>
   </si>
   <si>
-    <t>{.country}</t>
+    <t>{.countryName}</t>
   </si>
   <si>
     <t>{.provinceName}</t>
@@ -417,48 +348,6 @@
   </si>
   <si>
     <t>{.receiverTaxNo}</t>
-  </si>
-  <si>
-    <t>{.sourceFinanceAmount}</t>
-  </si>
-  <si>
-    <t>{.financeAmount}</t>
-  </si>
-  <si>
-    <t>{.sourceFinanceShippingCost}</t>
-  </si>
-  <si>
-    <t>{.financeShippingCost}</t>
-  </si>
-  <si>
-    <t>{.sourceItemCost}</t>
-  </si>
-  <si>
-    <t>{.itemCost}</t>
-  </si>
-  <si>
-    <t>{.sourceLogisticsCost}</t>
-  </si>
-  <si>
-    <t>{.logisticsCost}</t>
-  </si>
-  <si>
-    <t>{.sourcePlatformCost}</t>
-  </si>
-  <si>
-    <t>{.platformCost}</t>
-  </si>
-  <si>
-    <t>{.sourcePaypalCost}</t>
-  </si>
-  <si>
-    <t>{.paypalCost}</t>
-  </si>
-  <si>
-    <t>{.sourceVatCost}</t>
-  </si>
-  <si>
-    <t>{.vatCost}</t>
   </si>
 </sst>
 </file>
@@ -1392,7 +1281,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BR2"/>
+  <dimension ref="A1:BO2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1400,49 +1289,65 @@
     <col min="3" max="3" width="15.25" customWidth="1"/>
     <col min="4" max="4" width="17.375" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="12.875" customWidth="1"/>
-    <col min="7" max="7" width="15.125" customWidth="1"/>
-    <col min="8" max="8" width="18.625" customWidth="1"/>
-    <col min="9" max="9" width="14.625" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="14.125" customWidth="1"/>
-    <col min="13" max="13" width="13.75" customWidth="1"/>
-    <col min="14" max="14" width="13.875" customWidth="1"/>
-    <col min="15" max="15" width="14.875" customWidth="1"/>
-    <col min="17" max="17" width="10.5" customWidth="1"/>
-    <col min="22" max="22" width="12" customWidth="1"/>
-    <col min="23" max="23" width="11.875" customWidth="1"/>
-    <col min="25" max="25" width="16.25" customWidth="1"/>
-    <col min="27" max="27" width="14" customWidth="1"/>
-    <col min="28" max="28" width="12.875" customWidth="1"/>
-    <col min="29" max="29" width="13.125" customWidth="1"/>
-    <col min="30" max="30" width="13.375" customWidth="1"/>
-    <col min="36" max="36" width="12" customWidth="1"/>
-    <col min="37" max="37" width="12.375" customWidth="1"/>
-    <col min="38" max="38" width="10.375" customWidth="1"/>
-    <col min="42" max="42" width="10.625" customWidth="1"/>
-    <col min="44" max="44" width="9.875" customWidth="1"/>
-    <col min="46" max="46" width="11.25" customWidth="1"/>
-    <col min="54" max="54" width="11.25" customWidth="1"/>
-    <col min="55" max="55" width="17.125" customWidth="1"/>
-    <col min="56" max="56" width="12.125" customWidth="1"/>
-    <col min="57" max="57" width="12.75" customWidth="1"/>
-    <col min="58" max="58" width="10.75" customWidth="1"/>
-    <col min="59" max="59" width="12.25" customWidth="1"/>
-    <col min="60" max="60" width="11.625" customWidth="1"/>
-    <col min="61" max="61" width="11.375" customWidth="1"/>
-    <col min="62" max="62" width="11" customWidth="1"/>
-    <col min="63" max="63" width="10.875" customWidth="1"/>
-    <col min="64" max="64" width="11.125" customWidth="1"/>
-    <col min="65" max="65" width="10.25" customWidth="1"/>
-    <col min="66" max="66" width="12.25" customWidth="1"/>
-    <col min="67" max="67" width="12.75" customWidth="1"/>
-    <col min="68" max="68" width="11.875" customWidth="1"/>
-    <col min="69" max="69" width="11.5" customWidth="1"/>
+    <col min="6" max="6" width="18.625" customWidth="1"/>
+    <col min="7" max="8" width="14.625" customWidth="1"/>
+    <col min="9" max="9" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="13.75" customWidth="1"/>
+    <col min="11" max="11" width="13.875" customWidth="1"/>
+    <col min="12" max="12" width="14.875" customWidth="1"/>
+    <col min="14" max="14" width="16.5" customWidth="1"/>
+    <col min="15" max="15" width="17.875" customWidth="1"/>
+    <col min="17" max="17" width="14.25" customWidth="1"/>
+    <col min="18" max="18" width="17.75" customWidth="1"/>
+    <col min="19" max="19" width="13.125" customWidth="1"/>
+    <col min="20" max="20" width="15.875" customWidth="1"/>
+    <col min="21" max="21" width="15" customWidth="1"/>
+    <col min="22" max="22" width="17.375" customWidth="1"/>
+    <col min="23" max="23" width="19.375" customWidth="1"/>
+    <col min="24" max="24" width="14" customWidth="1"/>
+    <col min="25" max="25" width="12.875" customWidth="1"/>
+    <col min="26" max="26" width="22.125" customWidth="1"/>
+    <col min="27" max="27" width="13.375" customWidth="1"/>
+    <col min="28" max="28" width="18.5" customWidth="1"/>
+    <col min="30" max="30" width="11.375" customWidth="1"/>
+    <col min="32" max="32" width="17.625" customWidth="1"/>
+    <col min="33" max="33" width="12" customWidth="1"/>
+    <col min="34" max="34" width="12.375" customWidth="1"/>
+    <col min="35" max="35" width="10.375" customWidth="1"/>
+    <col min="36" max="36" width="11.375" customWidth="1"/>
+    <col min="37" max="37" width="10.5" customWidth="1"/>
+    <col min="38" max="38" width="11.125" customWidth="1"/>
+    <col min="39" max="39" width="15.25" customWidth="1"/>
+    <col min="40" max="40" width="16.25" customWidth="1"/>
+    <col min="41" max="41" width="14.375" customWidth="1"/>
+    <col min="42" max="42" width="15.125" customWidth="1"/>
+    <col min="43" max="43" width="17.625" customWidth="1"/>
+    <col min="44" max="44" width="22.375" customWidth="1"/>
+    <col min="45" max="45" width="15.125" customWidth="1"/>
+    <col min="46" max="46" width="15.625" customWidth="1"/>
+    <col min="47" max="47" width="15" customWidth="1"/>
+    <col min="48" max="48" width="14.125" customWidth="1"/>
+    <col min="49" max="49" width="16.75" customWidth="1"/>
+    <col min="50" max="50" width="13.25" customWidth="1"/>
+    <col min="51" max="51" width="14.375" customWidth="1"/>
+    <col min="52" max="52" width="17.125" customWidth="1"/>
+    <col min="53" max="53" width="17.25" customWidth="1"/>
+    <col min="54" max="54" width="16.375" customWidth="1"/>
+    <col min="55" max="55" width="14.375" customWidth="1"/>
+    <col min="56" max="56" width="18.125" customWidth="1"/>
+    <col min="57" max="57" width="16.25" customWidth="1"/>
+    <col min="58" max="58" width="15.125" customWidth="1"/>
+    <col min="59" max="59" width="17" customWidth="1"/>
+    <col min="60" max="60" width="15.75" customWidth="1"/>
+    <col min="61" max="61" width="14.625" customWidth="1"/>
+    <col min="62" max="62" width="14.125" customWidth="1"/>
+    <col min="63" max="63" width="17.375" customWidth="1"/>
+    <col min="64" max="64" width="17.25" customWidth="1"/>
+    <col min="65" max="65" width="15.625" customWidth="1"/>
+    <col min="66" max="66" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="54" spans="1:70">
+    <row r="1" ht="40.5" spans="1:67">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1470,7 +1375,7 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -1479,7 +1384,7 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
@@ -1497,22 +1402,22 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
       <c r="Y1" t="s">
@@ -1521,49 +1426,49 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>33</v>
       </c>
       <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" t="s">
         <v>40</v>
       </c>
       <c r="AP1" t="s">
@@ -1602,268 +1507,180 @@
       <c r="BA1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+    </row>
+    <row r="2" spans="1:53">
+      <c r="A2" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="B2" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="C2" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="D2" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="E2" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="F2" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="G2" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="H2" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="I2" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="J2" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="K2" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="L2" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="M2" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="N2" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="O2" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="P2" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="Q2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:70">
-      <c r="A2" t="s">
+      <c r="R2" t="s">
         <v>70</v>
       </c>
-      <c r="B2" t="s">
+      <c r="S2" t="s">
         <v>71</v>
       </c>
-      <c r="C2" t="s">
+      <c r="T2" t="s">
         <v>72</v>
       </c>
-      <c r="D2" t="s">
+      <c r="U2" t="s">
         <v>73</v>
       </c>
-      <c r="E2" t="s">
+      <c r="V2" t="s">
         <v>74</v>
       </c>
-      <c r="F2" t="s">
+      <c r="W2" t="s">
         <v>75</v>
       </c>
-      <c r="G2" t="s">
+      <c r="X2" t="s">
         <v>76</v>
       </c>
-      <c r="H2" t="s">
+      <c r="Y2" t="s">
         <v>77</v>
       </c>
-      <c r="I2" t="s">
+      <c r="Z2" t="s">
         <v>78</v>
       </c>
-      <c r="J2" t="s">
+      <c r="AA2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB2" t="s">
         <v>79</v>
       </c>
-      <c r="K2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="AC2" t="s">
         <v>80</v>
       </c>
-      <c r="M2" t="s">
+      <c r="AD2" t="s">
         <v>81</v>
       </c>
-      <c r="N2" t="s">
+      <c r="AE2" t="s">
         <v>82</v>
       </c>
-      <c r="O2" t="s">
+      <c r="AF2" t="s">
         <v>83</v>
       </c>
-      <c r="P2" t="s">
+      <c r="AG2" t="s">
         <v>84</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="AH2" t="s">
         <v>85</v>
       </c>
-      <c r="R2" t="s">
+      <c r="AI2" t="s">
         <v>86</v>
       </c>
-      <c r="S2" t="s">
+      <c r="AJ2" t="s">
         <v>87</v>
       </c>
-      <c r="T2" t="s">
+      <c r="AK2" t="s">
         <v>88</v>
       </c>
-      <c r="U2" t="s">
+      <c r="AL2" t="s">
         <v>89</v>
       </c>
-      <c r="V2" t="s">
+      <c r="AM2" t="s">
         <v>90</v>
       </c>
-      <c r="W2" t="s">
+      <c r="AN2" t="s">
         <v>91</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AO2" t="s">
         <v>92</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AP2" t="s">
         <v>93</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AQ2" t="s">
         <v>94</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AR2" t="s">
         <v>95</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AS2" t="s">
         <v>96</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AT2" t="s">
         <v>97</v>
       </c>
-      <c r="AD2" t="s">
-        <v>73</v>
-      </c>
-      <c r="AE2" t="s">
+      <c r="AU2" t="s">
         <v>98</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AV2" t="s">
         <v>99</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AW2" t="s">
         <v>100</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AX2" t="s">
         <v>101</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AY2" t="s">
         <v>102</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AZ2" t="s">
         <v>103</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="BA2" t="s">
         <v>104</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>106</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>109</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>111</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>113</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>120</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>121</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>126</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>128</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>129</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>130</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>131</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>133</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>134</v>
-      </c>
-      <c r="BP2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>136</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
@@ -296,13 +296,13 @@
     <t>{.accessoriesCost}</t>
   </si>
   <si>
-    <t>{.lengthStr}/cm</t>
-  </si>
-  <si>
-    <t>{.widthStr}/cm</t>
-  </si>
-  <si>
-    <t>{.heightStr}/cm</t>
+    <t>{.length}/cm</t>
+  </si>
+  <si>
+    <t>{.width}/cm</t>
+  </si>
+  <si>
+    <t>{.height}/cm</t>
   </si>
   <si>
     <t>{.loginId}</t>

--- a/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="107">
   <si>
     <t>销售单号</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>数量</t>
+  </si>
+  <si>
+    <t>SKU</t>
   </si>
   <si>
     <t>产品名称</t>
@@ -240,6 +243,9 @@
   </si>
   <si>
     <t>{.qty}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
   </si>
   <si>
     <t>{.productName}</t>
@@ -1281,7 +1287,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BO2"/>
+  <dimension ref="A1:BP2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1297,57 +1303,57 @@
     <col min="12" max="12" width="14.875" customWidth="1"/>
     <col min="14" max="14" width="16.5" customWidth="1"/>
     <col min="15" max="15" width="17.875" customWidth="1"/>
-    <col min="17" max="17" width="14.25" customWidth="1"/>
-    <col min="18" max="18" width="17.75" customWidth="1"/>
-    <col min="19" max="19" width="13.125" customWidth="1"/>
-    <col min="20" max="20" width="15.875" customWidth="1"/>
-    <col min="21" max="21" width="15" customWidth="1"/>
-    <col min="22" max="22" width="17.375" customWidth="1"/>
-    <col min="23" max="23" width="19.375" customWidth="1"/>
-    <col min="24" max="24" width="14" customWidth="1"/>
-    <col min="25" max="25" width="12.875" customWidth="1"/>
-    <col min="26" max="26" width="22.125" customWidth="1"/>
-    <col min="27" max="27" width="13.375" customWidth="1"/>
-    <col min="28" max="28" width="18.5" customWidth="1"/>
-    <col min="30" max="30" width="11.375" customWidth="1"/>
-    <col min="32" max="32" width="17.625" customWidth="1"/>
-    <col min="33" max="33" width="12" customWidth="1"/>
-    <col min="34" max="34" width="12.375" customWidth="1"/>
-    <col min="35" max="35" width="10.375" customWidth="1"/>
-    <col min="36" max="36" width="11.375" customWidth="1"/>
-    <col min="37" max="37" width="10.5" customWidth="1"/>
-    <col min="38" max="38" width="11.125" customWidth="1"/>
-    <col min="39" max="39" width="15.25" customWidth="1"/>
-    <col min="40" max="40" width="16.25" customWidth="1"/>
-    <col min="41" max="41" width="14.375" customWidth="1"/>
-    <col min="42" max="42" width="15.125" customWidth="1"/>
-    <col min="43" max="43" width="17.625" customWidth="1"/>
-    <col min="44" max="44" width="22.375" customWidth="1"/>
-    <col min="45" max="45" width="15.125" customWidth="1"/>
-    <col min="46" max="46" width="15.625" customWidth="1"/>
-    <col min="47" max="47" width="15" customWidth="1"/>
-    <col min="48" max="48" width="14.125" customWidth="1"/>
-    <col min="49" max="49" width="16.75" customWidth="1"/>
-    <col min="50" max="50" width="13.25" customWidth="1"/>
-    <col min="51" max="51" width="14.375" customWidth="1"/>
-    <col min="52" max="52" width="17.125" customWidth="1"/>
-    <col min="53" max="53" width="17.25" customWidth="1"/>
-    <col min="54" max="54" width="16.375" customWidth="1"/>
-    <col min="55" max="55" width="14.375" customWidth="1"/>
-    <col min="56" max="56" width="18.125" customWidth="1"/>
-    <col min="57" max="57" width="16.25" customWidth="1"/>
-    <col min="58" max="58" width="15.125" customWidth="1"/>
-    <col min="59" max="59" width="17" customWidth="1"/>
-    <col min="60" max="60" width="15.75" customWidth="1"/>
-    <col min="61" max="61" width="14.625" customWidth="1"/>
-    <col min="62" max="62" width="14.125" customWidth="1"/>
-    <col min="63" max="63" width="17.375" customWidth="1"/>
-    <col min="64" max="64" width="17.25" customWidth="1"/>
-    <col min="65" max="65" width="15.625" customWidth="1"/>
-    <col min="66" max="66" width="13.625" customWidth="1"/>
+    <col min="17" max="18" width="14.25" customWidth="1"/>
+    <col min="19" max="19" width="17.75" customWidth="1"/>
+    <col min="20" max="20" width="13.125" customWidth="1"/>
+    <col min="21" max="21" width="15.875" customWidth="1"/>
+    <col min="22" max="22" width="15" customWidth="1"/>
+    <col min="23" max="23" width="17.375" customWidth="1"/>
+    <col min="24" max="24" width="19.375" customWidth="1"/>
+    <col min="25" max="25" width="14" customWidth="1"/>
+    <col min="26" max="26" width="12.875" customWidth="1"/>
+    <col min="27" max="27" width="22.125" customWidth="1"/>
+    <col min="28" max="28" width="13.375" customWidth="1"/>
+    <col min="29" max="29" width="18.5" customWidth="1"/>
+    <col min="31" max="31" width="11.375" customWidth="1"/>
+    <col min="33" max="33" width="17.625" customWidth="1"/>
+    <col min="34" max="34" width="12" customWidth="1"/>
+    <col min="35" max="35" width="12.375" customWidth="1"/>
+    <col min="36" max="36" width="10.375" customWidth="1"/>
+    <col min="37" max="37" width="11.375" customWidth="1"/>
+    <col min="38" max="38" width="10.5" customWidth="1"/>
+    <col min="39" max="39" width="11.125" customWidth="1"/>
+    <col min="40" max="40" width="15.25" customWidth="1"/>
+    <col min="41" max="41" width="16.25" customWidth="1"/>
+    <col min="42" max="42" width="14.375" customWidth="1"/>
+    <col min="43" max="43" width="15.125" customWidth="1"/>
+    <col min="44" max="44" width="17.625" customWidth="1"/>
+    <col min="45" max="45" width="22.375" customWidth="1"/>
+    <col min="46" max="46" width="15.125" customWidth="1"/>
+    <col min="47" max="47" width="15.625" customWidth="1"/>
+    <col min="48" max="48" width="15" customWidth="1"/>
+    <col min="49" max="49" width="14.125" customWidth="1"/>
+    <col min="50" max="50" width="16.75" customWidth="1"/>
+    <col min="51" max="51" width="13.25" customWidth="1"/>
+    <col min="52" max="52" width="14.375" customWidth="1"/>
+    <col min="53" max="53" width="17.125" customWidth="1"/>
+    <col min="54" max="54" width="17.25" customWidth="1"/>
+    <col min="55" max="55" width="16.375" customWidth="1"/>
+    <col min="56" max="56" width="14.375" customWidth="1"/>
+    <col min="57" max="57" width="18.125" customWidth="1"/>
+    <col min="58" max="58" width="16.25" customWidth="1"/>
+    <col min="59" max="59" width="15.125" customWidth="1"/>
+    <col min="60" max="60" width="17" customWidth="1"/>
+    <col min="61" max="61" width="15.75" customWidth="1"/>
+    <col min="62" max="62" width="14.625" customWidth="1"/>
+    <col min="63" max="63" width="14.125" customWidth="1"/>
+    <col min="64" max="64" width="17.375" customWidth="1"/>
+    <col min="65" max="65" width="17.25" customWidth="1"/>
+    <col min="66" max="66" width="15.625" customWidth="1"/>
+    <col min="67" max="67" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:67">
+    <row r="1" ht="40.5" spans="1:68">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1402,7 +1408,7 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
@@ -1411,7 +1417,7 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
       <c r="W1" t="s">
@@ -1426,13 +1432,13 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
       <c r="AD1" s="1" t="s">
@@ -1441,7 +1447,7 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
       <c r="AG1" t="s">
@@ -1453,7 +1459,7 @@
       <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" t="s">
         <v>35</v>
       </c>
       <c r="AK1" s="1" t="s">
@@ -1462,7 +1468,7 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="AN1" t="s">
@@ -1507,7 +1513,9 @@
       <c r="BA1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="1"/>
+      <c r="BB1" t="s">
+        <v>53</v>
+      </c>
       <c r="BC1" s="1"/>
       <c r="BD1" s="1"/>
       <c r="BE1" s="1"/>
@@ -1521,166 +1529,170 @@
       <c r="BM1" s="1"/>
       <c r="BN1" s="1"/>
       <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
     </row>
-    <row r="2" spans="1:53">
+    <row r="2" spans="1:54">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O2" t="s">
+        <v>68</v>
+      </c>
+      <c r="P2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>70</v>
+      </c>
+      <c r="R2" t="s">
+        <v>71</v>
+      </c>
+      <c r="S2" t="s">
+        <v>72</v>
+      </c>
+      <c r="T2" t="s">
+        <v>73</v>
+      </c>
+      <c r="U2" t="s">
+        <v>74</v>
+      </c>
+      <c r="V2" t="s">
+        <v>75</v>
+      </c>
+      <c r="W2" t="s">
+        <v>76</v>
+      </c>
+      <c r="X2" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB2" t="s">
         <v>57</v>
       </c>
-      <c r="F2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K2" t="s">
-        <v>63</v>
-      </c>
-      <c r="L2" t="s">
-        <v>64</v>
-      </c>
-      <c r="M2" t="s">
-        <v>65</v>
-      </c>
-      <c r="N2" t="s">
-        <v>66</v>
-      </c>
-      <c r="O2" t="s">
-        <v>67</v>
-      </c>
-      <c r="P2" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>69</v>
-      </c>
-      <c r="R2" t="s">
-        <v>70</v>
-      </c>
-      <c r="S2" t="s">
-        <v>71</v>
-      </c>
-      <c r="T2" t="s">
-        <v>72</v>
-      </c>
-      <c r="U2" t="s">
-        <v>73</v>
-      </c>
-      <c r="V2" t="s">
-        <v>74</v>
-      </c>
-      <c r="W2" t="s">
-        <v>75</v>
-      </c>
-      <c r="X2" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>56</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>79</v>
-      </c>
       <c r="AC2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AD2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AE2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AF2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AG2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AH2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AK2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AL2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AM2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AN2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AO2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AP2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AQ2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AR2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AS2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AT2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AU2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AV2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AW2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AX2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AY2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AZ2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BA2" t="s">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="109">
   <si>
     <t>销售单号</t>
   </si>
@@ -74,10 +74,13 @@
     <t>平台SKU</t>
   </si>
   <si>
-    <t>数量</t>
+    <t>平台SKU数量</t>
   </si>
   <si>
     <t>SKU</t>
+  </si>
+  <si>
+    <t>SKU数量</t>
   </si>
   <si>
     <t>产品名称</t>
@@ -246,6 +249,9 @@
   </si>
   <si>
     <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.skuQty}</t>
   </si>
   <si>
     <t>{.productName}</t>
@@ -1287,7 +1293,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BP2"/>
+  <dimension ref="A1:BQ2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1303,57 +1309,58 @@
     <col min="12" max="12" width="14.875" customWidth="1"/>
     <col min="14" max="14" width="16.5" customWidth="1"/>
     <col min="15" max="15" width="17.875" customWidth="1"/>
-    <col min="17" max="18" width="14.25" customWidth="1"/>
-    <col min="19" max="19" width="17.75" customWidth="1"/>
-    <col min="20" max="20" width="13.125" customWidth="1"/>
-    <col min="21" max="21" width="15.875" customWidth="1"/>
-    <col min="22" max="22" width="15" customWidth="1"/>
-    <col min="23" max="23" width="17.375" customWidth="1"/>
-    <col min="24" max="24" width="19.375" customWidth="1"/>
-    <col min="25" max="25" width="14" customWidth="1"/>
-    <col min="26" max="26" width="12.875" customWidth="1"/>
-    <col min="27" max="27" width="22.125" customWidth="1"/>
-    <col min="28" max="28" width="13.375" customWidth="1"/>
-    <col min="29" max="29" width="18.5" customWidth="1"/>
-    <col min="31" max="31" width="11.375" customWidth="1"/>
-    <col min="33" max="33" width="17.625" customWidth="1"/>
-    <col min="34" max="34" width="12" customWidth="1"/>
-    <col min="35" max="35" width="12.375" customWidth="1"/>
-    <col min="36" max="36" width="10.375" customWidth="1"/>
-    <col min="37" max="37" width="11.375" customWidth="1"/>
-    <col min="38" max="38" width="10.5" customWidth="1"/>
-    <col min="39" max="39" width="11.125" customWidth="1"/>
-    <col min="40" max="40" width="15.25" customWidth="1"/>
-    <col min="41" max="41" width="16.25" customWidth="1"/>
-    <col min="42" max="42" width="14.375" customWidth="1"/>
-    <col min="43" max="43" width="15.125" customWidth="1"/>
-    <col min="44" max="44" width="17.625" customWidth="1"/>
-    <col min="45" max="45" width="22.375" customWidth="1"/>
-    <col min="46" max="46" width="15.125" customWidth="1"/>
-    <col min="47" max="47" width="15.625" customWidth="1"/>
-    <col min="48" max="48" width="15" customWidth="1"/>
-    <col min="49" max="49" width="14.125" customWidth="1"/>
-    <col min="50" max="50" width="16.75" customWidth="1"/>
-    <col min="51" max="51" width="13.25" customWidth="1"/>
-    <col min="52" max="52" width="14.375" customWidth="1"/>
-    <col min="53" max="53" width="17.125" customWidth="1"/>
-    <col min="54" max="54" width="17.25" customWidth="1"/>
-    <col min="55" max="55" width="16.375" customWidth="1"/>
-    <col min="56" max="56" width="14.375" customWidth="1"/>
-    <col min="57" max="57" width="18.125" customWidth="1"/>
-    <col min="58" max="58" width="16.25" customWidth="1"/>
-    <col min="59" max="59" width="15.125" customWidth="1"/>
-    <col min="60" max="60" width="17" customWidth="1"/>
-    <col min="61" max="61" width="15.75" customWidth="1"/>
-    <col min="62" max="62" width="14.625" customWidth="1"/>
-    <col min="63" max="63" width="14.125" customWidth="1"/>
-    <col min="64" max="64" width="17.375" customWidth="1"/>
-    <col min="65" max="65" width="17.25" customWidth="1"/>
-    <col min="66" max="66" width="15.625" customWidth="1"/>
-    <col min="67" max="67" width="13.625" customWidth="1"/>
+    <col min="16" max="16" width="12.75" customWidth="1"/>
+    <col min="17" max="19" width="14.25" customWidth="1"/>
+    <col min="20" max="20" width="17.75" customWidth="1"/>
+    <col min="21" max="21" width="13.125" customWidth="1"/>
+    <col min="22" max="22" width="15.875" customWidth="1"/>
+    <col min="23" max="23" width="15" customWidth="1"/>
+    <col min="24" max="24" width="17.375" customWidth="1"/>
+    <col min="25" max="25" width="19.375" customWidth="1"/>
+    <col min="26" max="26" width="14" customWidth="1"/>
+    <col min="27" max="27" width="12.875" customWidth="1"/>
+    <col min="28" max="28" width="22.125" customWidth="1"/>
+    <col min="29" max="29" width="13.375" customWidth="1"/>
+    <col min="30" max="30" width="18.5" customWidth="1"/>
+    <col min="32" max="32" width="11.375" customWidth="1"/>
+    <col min="34" max="34" width="17.625" customWidth="1"/>
+    <col min="35" max="35" width="12" customWidth="1"/>
+    <col min="36" max="36" width="12.375" customWidth="1"/>
+    <col min="37" max="37" width="10.375" customWidth="1"/>
+    <col min="38" max="38" width="11.375" customWidth="1"/>
+    <col min="39" max="39" width="10.5" customWidth="1"/>
+    <col min="40" max="40" width="11.125" customWidth="1"/>
+    <col min="41" max="41" width="15.25" customWidth="1"/>
+    <col min="42" max="42" width="16.25" customWidth="1"/>
+    <col min="43" max="43" width="14.375" customWidth="1"/>
+    <col min="44" max="44" width="15.125" customWidth="1"/>
+    <col min="45" max="45" width="17.625" customWidth="1"/>
+    <col min="46" max="46" width="22.375" customWidth="1"/>
+    <col min="47" max="47" width="15.125" customWidth="1"/>
+    <col min="48" max="48" width="15.625" customWidth="1"/>
+    <col min="49" max="49" width="15" customWidth="1"/>
+    <col min="50" max="50" width="14.125" customWidth="1"/>
+    <col min="51" max="51" width="16.75" customWidth="1"/>
+    <col min="52" max="52" width="13.25" customWidth="1"/>
+    <col min="53" max="53" width="14.375" customWidth="1"/>
+    <col min="54" max="54" width="17.125" customWidth="1"/>
+    <col min="55" max="55" width="17.25" customWidth="1"/>
+    <col min="56" max="56" width="16.375" customWidth="1"/>
+    <col min="57" max="57" width="14.375" customWidth="1"/>
+    <col min="58" max="58" width="18.125" customWidth="1"/>
+    <col min="59" max="59" width="16.25" customWidth="1"/>
+    <col min="60" max="60" width="15.125" customWidth="1"/>
+    <col min="61" max="61" width="17" customWidth="1"/>
+    <col min="62" max="62" width="15.75" customWidth="1"/>
+    <col min="63" max="63" width="14.625" customWidth="1"/>
+    <col min="64" max="64" width="14.125" customWidth="1"/>
+    <col min="65" max="65" width="17.375" customWidth="1"/>
+    <col min="66" max="66" width="17.25" customWidth="1"/>
+    <col min="67" max="67" width="15.625" customWidth="1"/>
+    <col min="68" max="68" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:68">
+    <row r="1" ht="40.5" spans="1:69">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1411,7 +1418,7 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
@@ -1420,7 +1427,7 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
       <c r="X1" t="s">
@@ -1435,13 +1442,13 @@
       <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="1" t="s">
@@ -1450,7 +1457,7 @@
       <c r="AF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
       <c r="AH1" t="s">
@@ -1462,7 +1469,7 @@
       <c r="AJ1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>36</v>
       </c>
       <c r="AL1" s="1" t="s">
@@ -1471,7 +1478,7 @@
       <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
       <c r="AO1" t="s">
@@ -1516,7 +1523,9 @@
       <c r="BB1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1"/>
+      <c r="BC1" t="s">
+        <v>54</v>
+      </c>
       <c r="BD1" s="1"/>
       <c r="BE1" s="1"/>
       <c r="BF1" s="1"/>
@@ -1530,169 +1539,173 @@
       <c r="BN1" s="1"/>
       <c r="BO1" s="1"/>
       <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
     </row>
-    <row r="2" spans="1:54">
+    <row r="2" spans="1:55">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N2" t="s">
+        <v>68</v>
+      </c>
+      <c r="O2" t="s">
+        <v>69</v>
+      </c>
+      <c r="P2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>71</v>
+      </c>
+      <c r="R2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S2" t="s">
+        <v>73</v>
+      </c>
+      <c r="T2" t="s">
+        <v>74</v>
+      </c>
+      <c r="U2" t="s">
+        <v>75</v>
+      </c>
+      <c r="V2" t="s">
+        <v>76</v>
+      </c>
+      <c r="W2" t="s">
+        <v>77</v>
+      </c>
+      <c r="X2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AC2" t="s">
         <v>58</v>
       </c>
-      <c r="F2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" t="s">
-        <v>62</v>
-      </c>
-      <c r="J2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L2" t="s">
-        <v>65</v>
-      </c>
-      <c r="M2" t="s">
-        <v>66</v>
-      </c>
-      <c r="N2" t="s">
-        <v>67</v>
-      </c>
-      <c r="O2" t="s">
-        <v>68</v>
-      </c>
-      <c r="P2" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>70</v>
-      </c>
-      <c r="R2" t="s">
-        <v>71</v>
-      </c>
-      <c r="S2" t="s">
-        <v>72</v>
-      </c>
-      <c r="T2" t="s">
-        <v>73</v>
-      </c>
-      <c r="U2" t="s">
-        <v>74</v>
-      </c>
-      <c r="V2" t="s">
-        <v>75</v>
-      </c>
-      <c r="W2" t="s">
-        <v>76</v>
-      </c>
-      <c r="X2" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>81</v>
-      </c>
       <c r="AD2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AF2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AG2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AJ2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AK2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AL2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AM2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AN2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AO2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AP2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AQ2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AR2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AT2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AU2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AV2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AW2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AX2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AY2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AZ2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="BA2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BB2" t="s">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
   <si>
     <t>销售单号</t>
   </si>
@@ -200,6 +200,9 @@
     <t>收件人税号</t>
   </si>
   <si>
+    <t>卖家订单编号</t>
+  </si>
+  <si>
     <t>{.code}</t>
   </si>
   <si>
@@ -360,6 +363,9 @@
   </si>
   <si>
     <t>{.receiverTaxNo}</t>
+  </si>
+  <si>
+    <t>{.sellerOrderCode}</t>
   </si>
 </sst>
 </file>
@@ -1345,7 +1351,7 @@
     <col min="53" max="53" width="14.375" customWidth="1"/>
     <col min="54" max="54" width="17.125" customWidth="1"/>
     <col min="55" max="55" width="17.25" customWidth="1"/>
-    <col min="56" max="56" width="16.375" customWidth="1"/>
+    <col min="56" max="56" width="19.375" customWidth="1"/>
     <col min="57" max="57" width="14.375" customWidth="1"/>
     <col min="58" max="58" width="18.125" customWidth="1"/>
     <col min="59" max="59" width="16.25" customWidth="1"/>
@@ -1526,7 +1532,9 @@
       <c r="BC1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="1"/>
+      <c r="BD1" t="s">
+        <v>55</v>
+      </c>
       <c r="BE1" s="1"/>
       <c r="BF1" s="1"/>
       <c r="BG1" s="1"/>
@@ -1541,171 +1549,174 @@
       <c r="BP1" s="1"/>
       <c r="BQ1" s="1"/>
     </row>
-    <row r="2" spans="1:55">
+    <row r="2" spans="1:56">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N2" t="s">
+        <v>69</v>
+      </c>
+      <c r="O2" t="s">
+        <v>70</v>
+      </c>
+      <c r="P2" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R2" t="s">
+        <v>73</v>
+      </c>
+      <c r="S2" t="s">
+        <v>74</v>
+      </c>
+      <c r="T2" t="s">
+        <v>75</v>
+      </c>
+      <c r="U2" t="s">
+        <v>76</v>
+      </c>
+      <c r="V2" t="s">
+        <v>77</v>
+      </c>
+      <c r="W2" t="s">
+        <v>78</v>
+      </c>
+      <c r="X2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AC2" t="s">
         <v>59</v>
       </c>
-      <c r="F2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L2" t="s">
-        <v>66</v>
-      </c>
-      <c r="M2" t="s">
-        <v>67</v>
-      </c>
-      <c r="N2" t="s">
-        <v>68</v>
-      </c>
-      <c r="O2" t="s">
-        <v>69</v>
-      </c>
-      <c r="P2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>71</v>
-      </c>
-      <c r="R2" t="s">
-        <v>72</v>
-      </c>
-      <c r="S2" t="s">
-        <v>73</v>
-      </c>
-      <c r="T2" t="s">
-        <v>74</v>
-      </c>
-      <c r="U2" t="s">
-        <v>75</v>
-      </c>
-      <c r="V2" t="s">
-        <v>76</v>
-      </c>
-      <c r="W2" t="s">
-        <v>77</v>
-      </c>
-      <c r="X2" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>58</v>
-      </c>
       <c r="AD2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AJ2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AK2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AL2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AM2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AN2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AO2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AP2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AR2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AS2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AT2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AU2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AV2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AW2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AX2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AY2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AZ2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="BA2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="BB2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="BC2" t="s">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/soB2c.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="115">
   <si>
     <t>销售单号</t>
   </si>
@@ -105,6 +105,12 @@
     <t>仓位</t>
   </si>
   <si>
+    <t>虚拟仓</t>
+  </si>
+  <si>
+    <t>虚拟仓可用库存</t>
+  </si>
+  <si>
     <t>买家备注</t>
   </si>
   <si>
@@ -276,6 +282,12 @@
   </si>
   <si>
     <t>{.warehouseLocationName}</t>
+  </si>
+  <si>
+    <t>{.virtualWarehouseName}</t>
+  </si>
+  <si>
+    <t>{.virtualUsableQty}</t>
   </si>
   <si>
     <t>{.buyerRemark}</t>
@@ -1299,7 +1311,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BQ2"/>
+  <dimension ref="A1:BS2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="12.125" customWidth="1"/>
@@ -1323,50 +1335,52 @@
     <col min="23" max="23" width="15" customWidth="1"/>
     <col min="24" max="24" width="17.375" customWidth="1"/>
     <col min="25" max="25" width="19.375" customWidth="1"/>
-    <col min="26" max="26" width="14" customWidth="1"/>
-    <col min="27" max="27" width="12.875" customWidth="1"/>
-    <col min="28" max="28" width="22.125" customWidth="1"/>
-    <col min="29" max="29" width="13.375" customWidth="1"/>
-    <col min="30" max="30" width="18.5" customWidth="1"/>
-    <col min="32" max="32" width="11.375" customWidth="1"/>
-    <col min="34" max="34" width="17.625" customWidth="1"/>
-    <col min="35" max="35" width="12" customWidth="1"/>
-    <col min="36" max="36" width="12.375" customWidth="1"/>
-    <col min="37" max="37" width="10.375" customWidth="1"/>
-    <col min="38" max="38" width="11.375" customWidth="1"/>
-    <col min="39" max="39" width="10.5" customWidth="1"/>
-    <col min="40" max="40" width="11.125" customWidth="1"/>
-    <col min="41" max="41" width="15.25" customWidth="1"/>
-    <col min="42" max="42" width="16.25" customWidth="1"/>
-    <col min="43" max="43" width="14.375" customWidth="1"/>
-    <col min="44" max="44" width="15.125" customWidth="1"/>
-    <col min="45" max="45" width="17.625" customWidth="1"/>
-    <col min="46" max="46" width="22.375" customWidth="1"/>
-    <col min="47" max="47" width="15.125" customWidth="1"/>
-    <col min="48" max="48" width="15.625" customWidth="1"/>
-    <col min="49" max="49" width="15" customWidth="1"/>
-    <col min="50" max="50" width="14.125" customWidth="1"/>
-    <col min="51" max="51" width="16.75" customWidth="1"/>
-    <col min="52" max="52" width="13.25" customWidth="1"/>
-    <col min="53" max="53" width="14.375" customWidth="1"/>
-    <col min="54" max="54" width="17.125" customWidth="1"/>
-    <col min="55" max="55" width="17.25" customWidth="1"/>
-    <col min="56" max="56" width="19.375" customWidth="1"/>
-    <col min="57" max="57" width="14.375" customWidth="1"/>
-    <col min="58" max="58" width="18.125" customWidth="1"/>
-    <col min="59" max="59" width="16.25" customWidth="1"/>
-    <col min="60" max="60" width="15.125" customWidth="1"/>
-    <col min="61" max="61" width="17" customWidth="1"/>
-    <col min="62" max="62" width="15.75" customWidth="1"/>
-    <col min="63" max="63" width="14.625" customWidth="1"/>
-    <col min="64" max="64" width="14.125" customWidth="1"/>
-    <col min="65" max="65" width="17.375" customWidth="1"/>
-    <col min="66" max="66" width="17.25" customWidth="1"/>
-    <col min="67" max="67" width="15.625" customWidth="1"/>
-    <col min="68" max="68" width="13.625" customWidth="1"/>
+    <col min="26" max="26" width="17.75" customWidth="1"/>
+    <col min="27" max="27" width="19.375" customWidth="1"/>
+    <col min="28" max="28" width="14" customWidth="1"/>
+    <col min="29" max="29" width="12.875" customWidth="1"/>
+    <col min="30" max="30" width="22.125" customWidth="1"/>
+    <col min="31" max="31" width="13.375" customWidth="1"/>
+    <col min="32" max="32" width="18.5" customWidth="1"/>
+    <col min="34" max="34" width="11.375" customWidth="1"/>
+    <col min="36" max="36" width="17.625" customWidth="1"/>
+    <col min="37" max="37" width="12" customWidth="1"/>
+    <col min="38" max="38" width="12.375" customWidth="1"/>
+    <col min="39" max="39" width="10.375" customWidth="1"/>
+    <col min="40" max="40" width="11.375" customWidth="1"/>
+    <col min="41" max="41" width="10.5" customWidth="1"/>
+    <col min="42" max="42" width="11.125" customWidth="1"/>
+    <col min="43" max="43" width="15.25" customWidth="1"/>
+    <col min="44" max="44" width="16.25" customWidth="1"/>
+    <col min="45" max="45" width="14.375" customWidth="1"/>
+    <col min="46" max="46" width="15.125" customWidth="1"/>
+    <col min="47" max="47" width="17.625" customWidth="1"/>
+    <col min="48" max="48" width="22.375" customWidth="1"/>
+    <col min="49" max="49" width="15.125" customWidth="1"/>
+    <col min="50" max="50" width="15.625" customWidth="1"/>
+    <col min="51" max="51" width="15" customWidth="1"/>
+    <col min="52" max="52" width="14.125" customWidth="1"/>
+    <col min="53" max="53" width="16.75" customWidth="1"/>
+    <col min="54" max="54" width="13.25" customWidth="1"/>
+    <col min="55" max="55" width="14.375" customWidth="1"/>
+    <col min="56" max="56" width="17.125" customWidth="1"/>
+    <col min="57" max="57" width="17.25" customWidth="1"/>
+    <col min="58" max="58" width="19.375" customWidth="1"/>
+    <col min="59" max="59" width="14.375" customWidth="1"/>
+    <col min="60" max="60" width="18.125" customWidth="1"/>
+    <col min="61" max="61" width="16.25" customWidth="1"/>
+    <col min="62" max="62" width="15.125" customWidth="1"/>
+    <col min="63" max="63" width="17" customWidth="1"/>
+    <col min="64" max="64" width="15.75" customWidth="1"/>
+    <col min="65" max="65" width="14.625" customWidth="1"/>
+    <col min="66" max="66" width="14.125" customWidth="1"/>
+    <col min="67" max="67" width="17.375" customWidth="1"/>
+    <col min="68" max="68" width="17.25" customWidth="1"/>
+    <col min="69" max="69" width="15.625" customWidth="1"/>
+    <col min="70" max="70" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.5" spans="1:69">
+    <row r="1" ht="40.5" spans="1:71">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1451,7 +1465,7 @@
       <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
       <c r="AD1" t="s">
@@ -1460,16 +1474,16 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" t="s">
@@ -1478,19 +1492,19 @@
       <c r="AK1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" t="s">
         <v>38</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>41</v>
       </c>
       <c r="AQ1" t="s">
@@ -1535,8 +1549,12 @@
       <c r="BD1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1"/>
-      <c r="BF1" s="1"/>
+      <c r="BE1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>57</v>
+      </c>
       <c r="BG1" s="1"/>
       <c r="BH1" s="1"/>
       <c r="BI1" s="1"/>
@@ -1548,175 +1566,183 @@
       <c r="BO1" s="1"/>
       <c r="BP1" s="1"/>
       <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:58">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S2" t="s">
+        <v>76</v>
+      </c>
+      <c r="T2" t="s">
+        <v>77</v>
+      </c>
+      <c r="U2" t="s">
+        <v>78</v>
+      </c>
+      <c r="V2" t="s">
+        <v>79</v>
+      </c>
+      <c r="W2" t="s">
+        <v>80</v>
+      </c>
+      <c r="X2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE2" t="s">
         <v>61</v>
       </c>
-      <c r="G2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I2" t="s">
-        <v>64</v>
-      </c>
-      <c r="J2" t="s">
-        <v>65</v>
-      </c>
-      <c r="K2" t="s">
-        <v>66</v>
-      </c>
-      <c r="L2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M2" t="s">
-        <v>68</v>
-      </c>
-      <c r="N2" t="s">
-        <v>69</v>
-      </c>
-      <c r="O2" t="s">
-        <v>70</v>
-      </c>
-      <c r="P2" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>72</v>
-      </c>
-      <c r="R2" t="s">
-        <v>73</v>
-      </c>
-      <c r="S2" t="s">
-        <v>74</v>
-      </c>
-      <c r="T2" t="s">
-        <v>75</v>
-      </c>
-      <c r="U2" t="s">
-        <v>76</v>
-      </c>
-      <c r="V2" t="s">
-        <v>77</v>
-      </c>
-      <c r="W2" t="s">
-        <v>78</v>
-      </c>
-      <c r="X2" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>85</v>
-      </c>
       <c r="AF2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AG2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AH2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AI2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AJ2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AL2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AM2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AN2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AO2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AP2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AQ2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AR2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AS2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AT2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AU2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AV2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AW2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AX2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AY2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AZ2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="BA2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BB2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="BC2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BD2" t="s">
-        <v>110</v>
+        <v>112</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>113</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
